--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\1.21.7\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50BAFFF3-6D03-45C0-98E8-DB7B0807BE1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{266EB93C-1AAC-46A7-8D5D-40C210FFFDCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Minecraft Version</t>
   </si>
@@ -73,6 +73,9 @@
   </si>
   <si>
     <t>Updated resource pack to work on 1.20 again</t>
+  </si>
+  <si>
+    <t>Fixed flowing water sound</t>
   </si>
 </sst>
 </file>
@@ -606,6 +609,11 @@
         <v>15</v>
       </c>
     </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
     <row r="21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:A24">

--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\1.21.7\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{266EB93C-1AAC-46A7-8D5D-40C210FFFDCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DC92BC2-4DF3-4160-AB00-E4D451BDAE30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -538,7 +538,7 @@
         <v>8</v>
       </c>
       <c r="C2" s="6">
-        <v>2508</v>
+        <v>2509</v>
       </c>
       <c r="D2" s="7"/>
       <c r="E2" s="7" t="s">

--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\1.21.7\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DC92BC2-4DF3-4160-AB00-E4D451BDAE30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3050BA4-9C3E-46B8-B1A7-C0B39DFC69E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Minecraft Version</t>
   </si>
@@ -57,25 +57,7 @@
     <t>Known issues (Compatibility)</t>
   </si>
   <si>
-    <t>Improved bat CEM</t>
-  </si>
-  <si>
-    <t>Improved boat CEM</t>
-  </si>
-  <si>
-    <t>Improved cat textures</t>
-  </si>
-  <si>
-    <t>Added a split shader channel for 1.21.9</t>
-  </si>
-  <si>
-    <t>Updated explosion particles 1.21.9+</t>
-  </si>
-  <si>
-    <t>Updated resource pack to work on 1.20 again</t>
-  </si>
-  <si>
-    <t>Fixed flowing water sound</t>
+    <t>Fixed AMD and Intel compatibility</t>
   </si>
 </sst>
 </file>
@@ -569,50 +551,28 @@
       <c r="H4" s="13"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>11</v>
-      </c>
       <c r="E5" s="13"/>
       <c r="F5" s="13"/>
       <c r="G5" s="13"/>
       <c r="H5" s="13"/>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="E6" s="13"/>
       <c r="F6" s="13"/>
       <c r="G6" s="13"/>
       <c r="H6" s="13"/>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="E7" s="13"/>
       <c r="F7" s="13"/>
       <c r="G7" s="13"/>
       <c r="H7" s="13"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
       <c r="H8" s="8"/>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>16</v>
-      </c>
     </row>
     <row r="21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>

--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\1.21.7\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3050BA4-9C3E-46B8-B1A7-C0B39DFC69E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95D3570C-C88B-4FBF-AA25-076D6F3179DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -45,9 +45,6 @@
     <t>1.21.9</t>
   </si>
   <si>
-    <t>OpenGL 4.5 and older (While the resource pack might be able to run, mods like ThreatenGL are highly recommended to run this resource pack, if your hardware does not support OpenGL 4.6 crashes might occur)</t>
-  </si>
-  <si>
     <t>VulkanMod compatibility (WIP)</t>
   </si>
   <si>
@@ -58,13 +55,16 @@
   </si>
   <si>
     <t>Fixed AMD and Intel compatibility</t>
+  </si>
+  <si>
+    <t>Fixed entity rendering (25w37a) Ims24</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -222,7 +222,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -486,13 +486,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H21"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.5"/>
   <cols>
-    <col min="1" max="5" width="18.28515625" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="5" width="18.25" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -506,75 +506,79 @@
         <v>3</v>
       </c>
       <c r="E1" s="11" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F1" s="12"/>
       <c r="G1" s="12"/>
       <c r="H1" s="12"/>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:8">
       <c r="A2" s="5" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2" s="6">
         <v>2509</v>
       </c>
       <c r="D2" s="7"/>
-      <c r="E2" s="7" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="E2" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+    </row>
+    <row r="3" spans="1:8" ht="16.5" customHeight="1">
       <c r="A3" s="9" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="10"/>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
-      <c r="E3" s="13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+    </row>
+    <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" s="8"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="E5" s="8"/>
+      <c r="F5" s="8"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="E6" s="8"/>
+      <c r="F6" s="8"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="E7" s="8"/>
+      <c r="F7" s="8"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+    </row>
+    <row r="8" spans="1:8">
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
       <c r="H8" s="8"/>
     </row>
-    <row r="21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="21" ht="16.5" customHeight="1"/>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:A24">
     <sortCondition ref="A24"/>
@@ -582,7 +586,7 @@
   <mergeCells count="3">
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="E1:H1"/>
-    <mergeCell ref="E3:H7"/>
+    <mergeCell ref="E2:H2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\1.21.7\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95D3570C-C88B-4FBF-AA25-076D6F3179DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{826F0C8E-41E2-496A-AC35-F1BD4DDDEDC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Minecraft Version</t>
   </si>
@@ -57,7 +57,13 @@
     <t>Fixed AMD and Intel compatibility</t>
   </si>
   <si>
-    <t>Fixed entity rendering (25w37a) Ims24</t>
+    <t>Fixed entity rendering in 1.21.9 (credits to Ims24)</t>
+  </si>
+  <si>
+    <t>Fixed entity lighting in 1.21.9</t>
+  </si>
+  <si>
+    <t>Ims24</t>
   </si>
 </sst>
 </file>
@@ -522,7 +528,9 @@
       <c r="C2" s="6">
         <v>2509</v>
       </c>
-      <c r="D2" s="7"/>
+      <c r="D2" s="7" t="s">
+        <v>12</v>
+      </c>
       <c r="E2" s="13" t="s">
         <v>6</v>
       </c>
@@ -561,6 +569,9 @@
       <c r="H5" s="8"/>
     </row>
     <row r="6" spans="1:8">
+      <c r="A6" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>

--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\1.21.7\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{826F0C8E-41E2-496A-AC35-F1BD4DDDEDC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA4888AA-3AB2-438E-9C27-30078CA7003C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Minecraft Version</t>
   </si>
@@ -64,6 +64,15 @@
   </si>
   <si>
     <t>Ims24</t>
+  </si>
+  <si>
+    <t>Improved entity clarity (1.21.9 fix)</t>
+  </si>
+  <si>
+    <t>Reimproved lightmap</t>
+  </si>
+  <si>
+    <t>Fixed vex texture</t>
   </si>
 </sst>
 </file>
@@ -526,7 +535,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="6">
-        <v>2509</v>
+        <v>2510</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>12</v>
@@ -578,16 +587,27 @@
       <c r="H6" s="8"/>
     </row>
     <row r="7" spans="1:8">
+      <c r="A7" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
     </row>
     <row r="8" spans="1:8">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
       <c r="H8" s="8"/>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" s="1" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="21" ht="16.5" customHeight="1"/>
   </sheetData>

--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\1.21.7\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AA4888AA-3AB2-438E-9C27-30078CA7003C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27BCA2B2-859A-4A41-865F-EFC4424CE5CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Minecraft Version</t>
   </si>
@@ -73,6 +73,9 @@
   </si>
   <si>
     <t>Fixed vex texture</t>
+  </si>
+  <si>
+    <t>Added Copper Horse Armor</t>
   </si>
 </sst>
 </file>
@@ -609,6 +612,11 @@
         <v>15</v>
       </c>
     </row>
+    <row r="10" spans="1:8">
+      <c r="A10" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
     <row r="21" ht="16.5" customHeight="1"/>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:A24">

--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\1.21.7\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27BCA2B2-859A-4A41-865F-EFC4424CE5CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C7D841A-24FB-4D9B-A4A1-B61F8633AA17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Minecraft Version</t>
   </si>
@@ -76,6 +76,9 @@
   </si>
   <si>
     <t>Added Copper Horse Armor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Changed copper golem textures </t>
   </si>
 </sst>
 </file>
@@ -617,6 +620,11 @@
         <v>16</v>
       </c>
     </row>
+    <row r="11" spans="1:8">
+      <c r="A11" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
     <row r="21" ht="16.5" customHeight="1"/>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:A24">

--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\1.21.7\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C7D841A-24FB-4D9B-A4A1-B61F8633AA17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{010CEF32-615D-4561-B239-5EE385861170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Minecraft Version</t>
   </si>
@@ -79,6 +79,9 @@
   </si>
   <si>
     <t xml:space="preserve">Changed copper golem textures </t>
+  </si>
+  <si>
+    <t>Changed night vision logic (1.21.9 required)</t>
   </si>
 </sst>
 </file>
@@ -567,7 +570,7 @@
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="1" t="s">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
@@ -576,7 +579,7 @@
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
@@ -585,7 +588,7 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
@@ -594,7 +597,7 @@
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
@@ -603,7 +606,7 @@
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="1" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
@@ -612,23 +615,28 @@
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" s="1" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="21" ht="16.5" customHeight="1"/>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:A24">
-    <sortCondition ref="A24"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:A12">
+    <sortCondition ref="A12"/>
   </sortState>
   <mergeCells count="3">
     <mergeCell ref="A3:B3"/>

--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\1.21.7\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{010CEF32-615D-4561-B239-5EE385861170}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14592853-B65B-4AE5-AACC-33900E7540D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -544,7 +544,7 @@
         <v>7</v>
       </c>
       <c r="C2" s="6">
-        <v>2510</v>
+        <v>3016</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>12</v>

--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -8,15 +8,26 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\1.21.7\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14592853-B65B-4AE5-AACC-33900E7540D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A60BCA5-CBAF-4B71-BD8D-AFF4FC26A509}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0" iterateDelta="1E-4"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -25,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Minecraft Version</t>
   </si>
@@ -54,34 +65,7 @@
     <t>Known issues (Compatibility)</t>
   </si>
   <si>
-    <t>Fixed AMD and Intel compatibility</t>
-  </si>
-  <si>
-    <t>Fixed entity rendering in 1.21.9 (credits to Ims24)</t>
-  </si>
-  <si>
-    <t>Fixed entity lighting in 1.21.9</t>
-  </si>
-  <si>
-    <t>Ims24</t>
-  </si>
-  <si>
-    <t>Improved entity clarity (1.21.9 fix)</t>
-  </si>
-  <si>
-    <t>Reimproved lightmap</t>
-  </si>
-  <si>
-    <t>Fixed vex texture</t>
-  </si>
-  <si>
-    <t>Added Copper Horse Armor</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Changed copper golem textures </t>
-  </si>
-  <si>
-    <t>Changed night vision logic (1.21.9 required)</t>
+    <t>None</t>
   </si>
 </sst>
 </file>
@@ -219,7 +203,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -242,11 +226,14 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -509,14 +496,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H21"/>
+  <dimension ref="A1:I21"/>
   <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="5" width="18.25" style="1" customWidth="1"/>
     <col min="6" max="16384" width="9.125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -532,11 +519,12 @@
       <c r="E1" s="11" t="s">
         <v>8</v>
       </c>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="F1" s="14"/>
+      <c r="G1" s="14"/>
+      <c r="H1" s="14"/>
+      <c r="I1" s="14"/>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="5" t="s">
         <v>5</v>
       </c>
@@ -544,104 +532,73 @@
         <v>7</v>
       </c>
       <c r="C2" s="6">
-        <v>3016</v>
+        <f>SUM(2510,507)</f>
+        <v>3017</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="13" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="13"/>
-      <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
-    </row>
-    <row r="3" spans="1:8" ht="16.5" customHeight="1">
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+    </row>
+    <row r="3" spans="1:9" ht="16.5" customHeight="1">
       <c r="A3" s="9" t="s">
         <v>4</v>
       </c>
       <c r="B3" s="10"/>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
-      <c r="E3" s="8"/>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
-    </row>
-    <row r="4" spans="1:8">
-      <c r="A4" s="1" t="s">
-        <v>16</v>
-      </c>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+    </row>
+    <row r="4" spans="1:9">
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
     </row>
-    <row r="5" spans="1:8">
-      <c r="A5" s="1" t="s">
-        <v>17</v>
-      </c>
+    <row r="5" spans="1:9">
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
     </row>
-    <row r="6" spans="1:8">
-      <c r="A6" s="1" t="s">
-        <v>18</v>
-      </c>
+    <row r="6" spans="1:9">
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
     </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
+    <row r="7" spans="1:9">
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
     </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="1" t="s">
-        <v>11</v>
-      </c>
+    <row r="8" spans="1:9">
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
       <c r="H8" s="8"/>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="A9" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="A10" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="A11" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
-      <c r="A12" s="1" t="s">
-        <v>14</v>
-      </c>
     </row>
     <row r="21" ht="16.5" customHeight="1"/>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:A12">
     <sortCondition ref="A12"/>
   </sortState>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="E1:H1"/>
-    <mergeCell ref="E2:H2"/>
+    <mergeCell ref="E3:I3"/>
+    <mergeCell ref="E2:I2"/>
+    <mergeCell ref="E1:I1"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\1.21.7\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A60BCA5-CBAF-4B71-BD8D-AFF4FC26A509}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17F20988-A8B6-426C-8E68-9B85C32BCE81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Minecraft Version</t>
   </si>
@@ -66,6 +66,9 @@
   </si>
   <si>
     <t>None</t>
+  </si>
+  <si>
+    <t>Removed blue color from nightvision</t>
   </si>
 </sst>
 </file>
@@ -223,16 +226,16 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -516,7 +519,7 @@
       <c r="D1" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="11" t="s">
+      <c r="E1" s="13" t="s">
         <v>8</v>
       </c>
       <c r="F1" s="14"/>
@@ -553,13 +556,16 @@
       <c r="B3" s="10"/>
       <c r="C3" s="7"/>
       <c r="D3" s="7"/>
-      <c r="E3" s="13"/>
-      <c r="F3" s="13"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-      <c r="I3" s="13"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11"/>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
     </row>
     <row r="4" spans="1:9">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>

--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\1.21.7\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17F20988-A8B6-426C-8E68-9B85C32BCE81}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCACACE5-FA2D-4AC8-ACDC-5456EE2F04B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Minecraft Version</t>
   </si>
@@ -69,13 +69,19 @@
   </si>
   <si>
     <t>Removed blue color from nightvision</t>
+  </si>
+  <si>
+    <t>Updated for 1.21.11</t>
+  </si>
+  <si>
+    <t>Added spear textures</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -500,13 +506,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I21"/>
-  <sheetFormatPr defaultColWidth="9.125" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="5" width="18.25" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.125" style="1"/>
+    <col min="1" max="5" width="18.28515625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -527,7 +533,7 @@
       <c r="H1" s="14"/>
       <c r="I1" s="14"/>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
         <v>5</v>
       </c>
@@ -549,7 +555,7 @@
       <c r="H2" s="12"/>
       <c r="I2" s="12"/>
     </row>
-    <row r="3" spans="1:9" ht="16.5" customHeight="1">
+    <row r="3" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="9" t="s">
         <v>4</v>
       </c>
@@ -562,43 +568,49 @@
       <c r="H3" s="11"/>
       <c r="I3" s="11"/>
     </row>
-    <row r="4" spans="1:9">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
     </row>
-    <row r="6" spans="1:9">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
       <c r="H8" s="8"/>
     </row>
-    <row r="21" ht="16.5" customHeight="1"/>
+    <row r="21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:A12">
-    <sortCondition ref="A12"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:A6">
+    <sortCondition ref="A4:A6"/>
   </sortState>
   <mergeCells count="4">
     <mergeCell ref="A3:B3"/>

--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\1.21.7\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BCACACE5-FA2D-4AC8-ACDC-5456EE2F04B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BEB8A28-106E-4094-AC5E-9109F61A2654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Minecraft Version</t>
   </si>
@@ -59,9 +59,6 @@
     <t>VulkanMod compatibility (WIP)</t>
   </si>
   <si>
-    <t>10.0.9-rt</t>
-  </si>
-  <si>
     <t>Known issues (Compatibility)</t>
   </si>
   <si>
@@ -75,6 +72,15 @@
   </si>
   <si>
     <t>Added spear textures</t>
+  </si>
+  <si>
+    <t>Fixed explosion sound</t>
+  </si>
+  <si>
+    <t>Fixed explosion particle</t>
+  </si>
+  <si>
+    <t>10.0.11-rt</t>
   </si>
 </sst>
 </file>
@@ -526,7 +532,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F1" s="14"/>
       <c r="G1" s="14"/>
@@ -538,14 +544,14 @@
         <v>5</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="C2" s="6">
-        <f>SUM(2510,507)</f>
-        <v>3017</v>
+        <f>SUM(2511,512,2025)</f>
+        <v>5048</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E2" s="12" t="s">
         <v>6</v>
@@ -570,7 +576,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
@@ -579,7 +585,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
@@ -588,7 +594,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
@@ -596,12 +602,18 @@
       <c r="H6" s="8"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>9</v>
+      </c>
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
@@ -609,8 +621,8 @@
     </row>
     <row r="21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:A6">
-    <sortCondition ref="A4:A6"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:A8">
+    <sortCondition ref="A8"/>
   </sortState>
   <mergeCells count="4">
     <mergeCell ref="A3:B3"/>

--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\1.21.7\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BEB8A28-106E-4094-AC5E-9109F61A2654}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3726ECF4-853B-446A-9098-A14C88D88C36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Minecraft Version</t>
   </si>
@@ -81,6 +81,12 @@
   </si>
   <si>
     <t>10.0.11-rt</t>
+  </si>
+  <si>
+    <t>Added json definitions for nautilus spawn egg</t>
+  </si>
+  <si>
+    <t>Added json definitions for zombie nautilus spawn egg</t>
   </si>
 </sst>
 </file>
@@ -547,8 +553,8 @@
         <v>14</v>
       </c>
       <c r="C2" s="6">
-        <f>SUM(2511,512,2025)</f>
-        <v>5048</v>
+        <f>SUM(2511,513,2025)</f>
+        <v>5049</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>8</v>
@@ -576,7 +582,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
@@ -585,7 +591,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
@@ -594,7 +600,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
@@ -603,7 +609,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
@@ -612,17 +618,27 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
       <c r="H8" s="8"/>
     </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
     <row r="21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:A8">
-    <sortCondition ref="A8"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:A10">
+    <sortCondition ref="A10"/>
   </sortState>
   <mergeCells count="4">
     <mergeCell ref="A3:B3"/>

--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\1.21.7\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3726ECF4-853B-446A-9098-A14C88D88C36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6524F0A3-525F-400F-875C-4CA7CDA77015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Minecraft Version</t>
   </si>
@@ -87,6 +87,9 @@
   </si>
   <si>
     <t>Added json definitions for zombie nautilus spawn egg</t>
+  </si>
+  <si>
+    <t>Downgraded Classic Reimagined 7 to fix stability issues on Lenovo ThinkPads</t>
   </si>
 </sst>
 </file>
@@ -635,6 +638,11 @@
         <v>10</v>
       </c>
     </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
     <row r="21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:A10">

--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\1.21.7\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6524F0A3-525F-400F-875C-4CA7CDA77015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9F81AB5-ED25-47CA-885A-5E795EE20607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Minecraft Version</t>
   </si>
@@ -90,6 +90,9 @@
   </si>
   <si>
     <t>Downgraded Classic Reimagined 7 to fix stability issues on Lenovo ThinkPads</t>
+  </si>
+  <si>
+    <t>Added nautilus armor item textures</t>
   </si>
 </sst>
 </file>
@@ -643,6 +646,11 @@
         <v>17</v>
       </c>
     </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
     <row r="21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:A10">

--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\1.21.7\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9F81AB5-ED25-47CA-885A-5E795EE20607}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{772D07B1-5289-468D-9742-6565CE250F55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>Minecraft Version</t>
   </si>
@@ -93,6 +93,9 @@
   </si>
   <si>
     <t>Added nautilus armor item textures</t>
+  </si>
+  <si>
+    <t>Added texture for nautilus saddle</t>
   </si>
 </sst>
 </file>
@@ -559,8 +562,8 @@
         <v>14</v>
       </c>
       <c r="C2" s="6">
-        <f>SUM(2511,513,2025)</f>
-        <v>5049</v>
+        <f>SUM(2511,524,2025)</f>
+        <v>5060</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>8</v>
@@ -606,7 +609,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
@@ -615,7 +618,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
@@ -624,7 +627,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
@@ -633,28 +636,33 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>9</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:A10">
-    <sortCondition ref="A10"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:A13">
+    <sortCondition ref="A13"/>
   </sortState>
   <mergeCells count="4">
     <mergeCell ref="A3:B3"/>

--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\1.21.7\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{772D07B1-5289-468D-9742-6565CE250F55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB2ED57-2ED6-4C4C-A8E5-6AD609D7DE43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -53,9 +53,6 @@
     <t>Changes done!</t>
   </si>
   <si>
-    <t>1.21.9</t>
-  </si>
-  <si>
     <t>VulkanMod compatibility (WIP)</t>
   </si>
   <si>
@@ -80,9 +77,6 @@
     <t>Fixed explosion particle</t>
   </si>
   <si>
-    <t>10.0.11-rt</t>
-  </si>
-  <si>
     <t>Added json definitions for nautilus spawn egg</t>
   </si>
   <si>
@@ -96,6 +90,12 @@
   </si>
   <si>
     <t>Added texture for nautilus saddle</t>
+  </si>
+  <si>
+    <t>10.0.10-rt</t>
+  </si>
+  <si>
+    <t>1.21.11</t>
   </si>
 </sst>
 </file>
@@ -547,7 +547,7 @@
         <v>3</v>
       </c>
       <c r="E1" s="13" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F1" s="14"/>
       <c r="G1" s="14"/>
@@ -556,20 +556,20 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="C2" s="6">
         <f>SUM(2511,524,2025)</f>
         <v>5060</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E2" s="12" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" s="12"/>
       <c r="G2" s="12"/>
@@ -591,7 +591,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
@@ -600,7 +600,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
@@ -609,7 +609,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
@@ -618,7 +618,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
@@ -627,7 +627,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
@@ -636,27 +636,27 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\1.21.7\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BB2ED57-2ED6-4C4C-A8E5-6AD609D7DE43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0A45007-8575-49DA-BE90-8E293B16AEC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -562,8 +562,8 @@
         <v>18</v>
       </c>
       <c r="C2" s="6">
-        <f>SUM(2511,524,2025)</f>
-        <v>5060</v>
+        <f>SUM(2511,526,2025)</f>
+        <v>5062</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>7</v>

--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\1.21.7\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0A45007-8575-49DA-BE90-8E293B16AEC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C81D17BE-CAF5-48D5-9B06-2122F5AD95D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\1.21.7\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C81D17BE-CAF5-48D5-9B06-2122F5AD95D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C98D3386-16E5-400C-8B14-FEF52DD436F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -562,8 +562,8 @@
         <v>18</v>
       </c>
       <c r="C2" s="6">
-        <f>SUM(2511,526,2025)</f>
-        <v>5062</v>
+        <f>SUM(2511,527,2025)</f>
+        <v>5063</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>7</v>

--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\1.21.7\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C98D3386-16E5-400C-8B14-FEF52DD436F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BEECEA9-3E4F-4CCE-82F0-EDA28317D199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>Minecraft Version</t>
   </si>
@@ -96,6 +96,9 @@
   </si>
   <si>
     <t>1.21.11</t>
+  </si>
+  <si>
+    <t>Improved glass mipmapping</t>
   </si>
 </sst>
 </file>
@@ -659,6 +662,11 @@
         <v>9</v>
       </c>
     </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
     <row r="21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:A13">

--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\1.21.7\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1BEECEA9-3E4F-4CCE-82F0-EDA28317D199}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35A19C59-F7DA-4D26-96E1-38E20E75D7B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Minecraft Version</t>
   </si>
@@ -99,6 +99,9 @@
   </si>
   <si>
     <t>Improved glass mipmapping</t>
+  </si>
+  <si>
+    <t>Added assets for mutant monsters mod</t>
   </si>
 </sst>
 </file>
@@ -565,8 +568,8 @@
         <v>18</v>
       </c>
       <c r="C2" s="6">
-        <f>SUM(2511,527,2025)</f>
-        <v>5063</v>
+        <f>SUM(2511,532,2025)</f>
+        <v>5068</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>7</v>
@@ -594,7 +597,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
@@ -603,7 +606,7 @@
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
@@ -612,7 +615,7 @@
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
@@ -621,7 +624,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
@@ -630,7 +633,7 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
@@ -639,38 +642,43 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A15" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:A13">
-    <sortCondition ref="A13"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:A15">
+    <sortCondition ref="A15"/>
   </sortState>
   <mergeCells count="4">
     <mergeCell ref="A3:B3"/>

--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\1.21.7\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35A19C59-F7DA-4D26-96E1-38E20E75D7B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{287CF909-42A6-424A-8F31-0AC1C03CD200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
   <si>
     <t>Minecraft Version</t>
   </si>
@@ -568,8 +568,8 @@
         <v>18</v>
       </c>
       <c r="C2" s="6">
-        <f>SUM(2511,532,2025)</f>
-        <v>5068</v>
+        <f>SUM(2511,536,2025)</f>
+        <v>5072</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>7</v>
@@ -657,28 +657,33 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>20</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A16" s="1" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:A15">
-    <sortCondition ref="A15"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:A16">
+    <sortCondition ref="A16"/>
   </sortState>
   <mergeCells count="4">
     <mergeCell ref="A3:B3"/>

--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\1.21.7\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{287CF909-42A6-424A-8F31-0AC1C03CD200}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80B5C4CC-D952-4391-B1C3-BC04CF90110E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -83,9 +83,6 @@
     <t>Added json definitions for zombie nautilus spawn egg</t>
   </si>
   <si>
-    <t>Downgraded Classic Reimagined 7 to fix stability issues on Lenovo ThinkPads</t>
-  </si>
-  <si>
     <t>Added nautilus armor item textures</t>
   </si>
   <si>
@@ -102,6 +99,9 @@
   </si>
   <si>
     <t>Added assets for mutant monsters mod</t>
+  </si>
+  <si>
+    <t>Downgraded Classic Reimagined 7 to fix compatibility issues on Lenovo ThinkPads</t>
   </si>
 </sst>
 </file>
@@ -562,14 +562,14 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C2" s="6">
-        <f>SUM(2511,536,2025)</f>
-        <v>5072</v>
+        <f>SUM(2511,538,2025)</f>
+        <v>5074</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>7</v>
@@ -597,7 +597,7 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
@@ -624,7 +624,7 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
@@ -642,12 +642,12 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
@@ -667,7 +667,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.3">

--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\1.21.7\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80B5C4CC-D952-4391-B1C3-BC04CF90110E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{744B5A16-913E-4C27-89D2-433D313DB5F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>Minecraft Version</t>
   </si>
@@ -62,46 +62,10 @@
     <t>None</t>
   </si>
   <si>
-    <t>Removed blue color from nightvision</t>
-  </si>
-  <si>
-    <t>Updated for 1.21.11</t>
-  </si>
-  <si>
-    <t>Added spear textures</t>
-  </si>
-  <si>
-    <t>Fixed explosion sound</t>
-  </si>
-  <si>
-    <t>Fixed explosion particle</t>
-  </si>
-  <si>
-    <t>Added json definitions for nautilus spawn egg</t>
-  </si>
-  <si>
-    <t>Added json definitions for zombie nautilus spawn egg</t>
-  </si>
-  <si>
-    <t>Added nautilus armor item textures</t>
-  </si>
-  <si>
-    <t>Added texture for nautilus saddle</t>
-  </si>
-  <si>
     <t>10.0.10-rt</t>
   </si>
   <si>
     <t>1.21.11</t>
-  </si>
-  <si>
-    <t>Improved glass mipmapping</t>
-  </si>
-  <si>
-    <t>Added assets for mutant monsters mod</t>
-  </si>
-  <si>
-    <t>Downgraded Classic Reimagined 7 to fix compatibility issues on Lenovo ThinkPads</t>
   </si>
 </sst>
 </file>
@@ -562,14 +526,14 @@
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A2" s="5" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="C2" s="6">
-        <f>SUM(2511,538,2025)</f>
-        <v>5074</v>
+        <f>SUM(2511,539,2025)</f>
+        <v>5075</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>7</v>
@@ -596,89 +560,34 @@
       <c r="I3" s="11"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>20</v>
-      </c>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>13</v>
-      </c>
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
       <c r="G5" s="8"/>
       <c r="H5" s="8"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>14</v>
-      </c>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
       <c r="H6" s="8"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>15</v>
-      </c>
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>10</v>
-      </c>
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
       <c r="H8" s="8"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
-        <v>9</v>
-      </c>
     </row>
     <row r="21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>

--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\1.21.7\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{744B5A16-913E-4C27-89D2-433D313DB5F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E33235CC-0C5A-4332-8868-AB32C7C66F31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>Minecraft Version</t>
   </si>
@@ -66,6 +66,9 @@
   </si>
   <si>
     <t>1.21.11</t>
+  </si>
+  <si>
+    <t>Updated CEM (full fix for boats)</t>
   </si>
 </sst>
 </file>
@@ -560,6 +563,9 @@
       <c r="I3" s="11"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
       <c r="E4" s="8"/>
       <c r="F4" s="8"/>
       <c r="G4" s="8"/>

--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\1.21.7\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E33235CC-0C5A-4332-8868-AB32C7C66F31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7684896F-3B5F-497E-8D08-A67ACDDCDB32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>Minecraft Version</t>
   </si>
@@ -69,6 +69,9 @@
   </si>
   <si>
     <t>Updated CEM (full fix for boats)</t>
+  </si>
+  <si>
+    <t>Added chest CEM (WIP)</t>
   </si>
 </sst>
 </file>
@@ -535,8 +538,8 @@
         <v>8</v>
       </c>
       <c r="C2" s="6">
-        <f>SUM(2511,539,2025)</f>
-        <v>5075</v>
+        <f>SUM(2511,544,2025)</f>
+        <v>5080</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>7</v>
@@ -572,6 +575,9 @@
       <c r="H4" s="8"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A5" s="1" t="s">
+        <v>11</v>
+      </c>
       <c r="E5" s="8"/>
       <c r="F5" s="8"/>
       <c r="G5" s="8"/>

--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\1.21.7\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7684896F-3B5F-497E-8D08-A67ACDDCDB32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0003C4D-2D84-4E93-BBBE-BDC2514A89B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
   <si>
     <t>Minecraft Version</t>
   </si>
@@ -72,6 +72,9 @@
   </si>
   <si>
     <t>Added chest CEM (WIP)</t>
+  </si>
+  <si>
+    <t>Added sprites for mod menu buttons</t>
   </si>
 </sst>
 </file>
@@ -538,8 +541,8 @@
         <v>8</v>
       </c>
       <c r="C2" s="6">
-        <f>SUM(2511,544,2025)</f>
-        <v>5080</v>
+        <f>SUM(2511,548,2025)</f>
+        <v>5084</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>7</v>
@@ -584,6 +587,9 @@
       <c r="H5" s="8"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>12</v>
+      </c>
       <c r="E6" s="8"/>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>

--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\1.21.7\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0003C4D-2D84-4E93-BBBE-BDC2514A89B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D525509F-0EA1-42D4-9F12-8389394ED83A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Minecraft Version</t>
   </si>
@@ -75,6 +75,12 @@
   </si>
   <si>
     <t>Added sprites for mod menu buttons</t>
+  </si>
+  <si>
+    <t>Updated stained terracotta textures</t>
+  </si>
+  <si>
+    <t>Updated anvil textures</t>
   </si>
 </sst>
 </file>
@@ -541,8 +547,8 @@
         <v>8</v>
       </c>
       <c r="C2" s="6">
-        <f>SUM(2511,548,2025)</f>
-        <v>5084</v>
+        <f>SUM(2511,551,2025)</f>
+        <v>5087</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>7</v>
@@ -596,12 +602,18 @@
       <c r="H6" s="8"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>13</v>
+      </c>
       <c r="E7" s="8"/>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
       <c r="H7" s="8"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
+        <v>14</v>
+      </c>
       <c r="E8" s="8"/>
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>

--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\1.21.7\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D525509F-0EA1-42D4-9F12-8389394ED83A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF744504-A977-4658-B0D5-E786F00908E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>Minecraft Version</t>
   </si>
@@ -81,6 +81,9 @@
   </si>
   <si>
     <t>Updated anvil textures</t>
+  </si>
+  <si>
+    <t>Changed brewing stand texture</t>
   </si>
 </sst>
 </file>
@@ -619,6 +622,11 @@
       <c r="G8" s="8"/>
       <c r="H8" s="8"/>
     </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
     <row r="21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:A16">

--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\1.21.7\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF744504-A977-4658-B0D5-E786F00908E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9F53E22-0BC7-4BF6-A7C8-8C871F2BC852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Minecraft Version</t>
   </si>
@@ -84,6 +84,12 @@
   </si>
   <si>
     <t>Changed brewing stand texture</t>
+  </si>
+  <si>
+    <t>Fixed lightmaps for 25w44a snapshot</t>
+  </si>
+  <si>
+    <t>Updated pack.mcmeta</t>
   </si>
 </sst>
 </file>
@@ -627,6 +633,16 @@
         <v>15</v>
       </c>
     </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
     <row r="21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:A16">

--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\1.21.7\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9F53E22-0BC7-4BF6-A7C8-8C871F2BC852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC443E56-45F3-416F-B88F-D57734A37C62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -556,8 +556,8 @@
         <v>8</v>
       </c>
       <c r="C2" s="6">
-        <f>SUM(2511,551,2025)</f>
-        <v>5087</v>
+        <f>SUM(2511,556,2025)</f>
+        <v>5092</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>7</v>

--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\1.21.7\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FC443E56-45F3-416F-B88F-D57734A37C62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AC5CA10-2F8D-4ABB-B60C-958E51999461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Minecraft Version</t>
   </si>
@@ -90,6 +90,9 @@
   </si>
   <si>
     <t>Updated pack.mcmeta</t>
+  </si>
+  <si>
+    <t>Added Parched texture</t>
   </si>
 </sst>
 </file>
@@ -556,8 +559,8 @@
         <v>8</v>
       </c>
       <c r="C2" s="6">
-        <f>SUM(2511,556,2025)</f>
-        <v>5092</v>
+        <f>SUM(2511,558,2025)</f>
+        <v>5094</v>
       </c>
       <c r="D2" s="7" t="s">
         <v>7</v>
@@ -641,6 +644,11 @@
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>

--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\1.21.7\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5AC5CA10-2F8D-4ABB-B60C-958E51999461}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40763ED6-3B43-4E37-A3A0-F3FE071CF0E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -62,9 +62,6 @@
     <t>None</t>
   </si>
   <si>
-    <t>10.0.10-rt</t>
-  </si>
-  <si>
     <t>1.21.11</t>
   </si>
   <si>
@@ -93,13 +90,16 @@
   </si>
   <si>
     <t>Added Parched texture</t>
+  </si>
+  <si>
+    <t>10.0.10</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -129,19 +129,20 @@
       <family val="2"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00FF00"/>
-        <bgColor rgb="FF33CCCC"/>
-      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -168,7 +169,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -197,19 +198,8 @@
       </left>
       <right/>
       <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -218,9 +208,7 @@
       <right style="thin">
         <color auto="1"/>
       </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
+      <top/>
       <bottom style="thin">
         <color auto="1"/>
       </bottom>
@@ -230,37 +218,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -526,129 +506,127 @@
   <dimension ref="A1:I21"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="5" width="18.28515625" style="1" customWidth="1"/>
+    <col min="1" max="2" width="18.28515625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="27.42578125" style="1" customWidth="1"/>
+    <col min="4" max="5" width="18.28515625" style="1" customWidth="1"/>
     <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
+      <c r="F1" s="8"/>
+      <c r="G1" s="8"/>
+      <c r="H1" s="8"/>
+      <c r="I1" s="8"/>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="5" t="s">
+      <c r="A2" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="9">
+        <f>SUM(2511,559,2025)</f>
+        <v>5095</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="6">
-        <f>SUM(2511,558,2025)</f>
-        <v>5094</v>
-      </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="12" t="s">
+      <c r="E2" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
     </row>
     <row r="3" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="9" t="s">
+      <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="10"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="11"/>
-      <c r="H3" s="11"/>
-      <c r="I3" s="11"/>
+      <c r="B3" s="6"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="E4" s="8"/>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
+        <v>9</v>
+      </c>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="8"/>
-      <c r="F5" s="8"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
+        <v>10</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="8"/>
-      <c r="F6" s="8"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
+        <v>11</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="8"/>
-      <c r="F7" s="8"/>
-      <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
+        <v>12</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="8"/>
-      <c r="F8" s="8"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
+        <v>13</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -656,11 +634,10 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:A16">
     <sortCondition ref="A16"/>
   </sortState>
-  <mergeCells count="4">
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="E3:I3"/>
+  <mergeCells count="3">
     <mergeCell ref="E2:I2"/>
     <mergeCell ref="E1:I1"/>
+    <mergeCell ref="A3:B3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>

--- a/changelog.xlsx
+++ b/changelog.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PrismLauncher\instances\1.21.7\minecraft\resourcepacks\Classic-Reimagined\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40763ED6-3B43-4E37-A3A0-F3FE071CF0E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAF40470-A38E-4306-BC58-5AD26300743D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
   <si>
     <t>Minecraft Version</t>
   </si>
@@ -93,6 +93,9 @@
   </si>
   <si>
     <t>10.0.10</t>
+  </si>
+  <si>
+    <t>Fixed texture fidelity for 25w44a snapshot</t>
   </si>
 </sst>
 </file>
@@ -226,21 +229,21 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -522,7 +525,7 @@
       <c r="C1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="8" t="s">
@@ -537,9 +540,9 @@
       <c r="A2" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B2" s="9">
-        <f>SUM(2511,559,2025)</f>
-        <v>5095</v>
+      <c r="B2" s="6">
+        <f>SUM(2511,561,2025)</f>
+        <v>5097</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>8</v>
@@ -547,19 +550,19 @@
       <c r="D2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="10" t="s">
+      <c r="E2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
     </row>
     <row r="3" spans="1:9" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="6"/>
+      <c r="B3" s="10"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
@@ -627,6 +630,11 @@
     <row r="12" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="1" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="21" ht="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
